--- a/storage/workspaces/facturas/documents/Facturas_totales.xlsx
+++ b/storage/workspaces/facturas/documents/Facturas_totales.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1741,4137 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>davallejos</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pro-WRFPjWvD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1260-17067674</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>30/06/2025</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>27422260930</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Responsable Monotributo</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Erezcano 1029 - Adrogue, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>30-27114647-0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Responsabe Inscripto</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Av Rivadavia 12980
+Ciudadela, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios de diseño grafico y manejo de redes) (importe: 750000.00) (subtotal: 750000.00) (monto_preferido: 750000.00) }</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>750000</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>157500</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>48800000000000</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>davallejos</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pro-pjdyW26p</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7027-83357158</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>28/06/2025</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>33690789499</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Av. Caseros 6178, CABA, CP 1322, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios) (importe: 1734000.00) (subtotal: 1734000) (monto_preferido: 1734000) }</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1734000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>364140</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>20300000000000</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>07/08/2025</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>davallejos</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>pro-rpGQFEYN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0300-25808736</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>05/12/2023</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>30703948983</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Av. Belgrano 9018, CABA, CP 1511, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>67799900000000</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>22/05/2023</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>davallejos</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pro-ZWo4ZPEQ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0005-27133733</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>30741612341</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Av. Santa Fe 410, CABA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>30526124916</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Carlos Maria Della Paolera 261 - 4º piso C1001ADA - C.A.B.A. - Argentina</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>{ (detalle: 1×2.395, 87 / 20) (importe: 2300.70) (alicuota_iva: 20) (alicuota_iva_fuente: detalle) (importe_iva_calc: 460.14) (monto_preferido: 2300.70) } { (detalle: 6×2 . 2726×2 . 272) (importe: 13636.36) (alicuota_iva: 2) (alicuota_iva_fuente: detalle) (importe_iva_calc: 272.73) (monto_preferido: 13636.36) }</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>15.937,06</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3.346,78</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>478,11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ovenpereyraatgmail.com</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1000052444</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3183-82653424</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>15/04/2025</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>33715065539</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Av. San Juan 2893, 1322, CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Responsable inscripto</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>{ (detalle: SERVICIOS) (importe: 3161676.408) (subtotal: 3161676.41) (monto_preferido: 3161676.41) }</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3.161.676,41</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>663952,05</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>81109500000000</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>25/04/2025</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ovenpereyraatgmail.com</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1000052443</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5742-70241789</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>07/01/2025</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>30597318584</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>IVA Responsable</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Av. Santa Fe 3400, CABA (C1425MNO)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>30-22090099-5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>IVA Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>General Munilla 981
+Moron, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios de Arriendo) (importe: 001734000) (monto_preferido: 001734000) }</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1734000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>364140</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>41900000000000</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>camquirog01atgmail.com</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0880</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0982-93725968</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>30656760172</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Av. Independencia 1450 C1009ABQ-Capital Federal</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Incripto</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios asesoramiento contable) (importe: 500000) (subtotal: 500000.00) (monto_preferido: 500000.00) }</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>500.000,00</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>105.000,00</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>81.766.435.916.696,00</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>16/06/2025</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>camquirog01atgmail.com</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0882</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>3015-78786186</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>15/05/2023</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>30715636545</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>I.V.A. Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Av. Corrientes 2540 (C1016ACA) Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Incripto</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>{ (detalle: Monthly services PO#8500XX 0001) (importe: 900) (subtotal: 900.00) (alicuota_iva: 0001) (alicuota_iva_fuente: detalle) (importe_iva_calc: 9.00) (monto_preferido: 900.00) }</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>900,00</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>189,00</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>76513578458796</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>25/05/2023</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>camquirog01atgmail.com</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0881</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0300-43869861</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>19/05/2023</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>30703948983</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Av. Belgrano 9018, CABA, CP 1511, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>88483300000000</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>29/05/2023</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>camquirog01atgmail.com</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0883</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>7027-41242102</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>28/06/2025</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>33690789499</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Av. Caseros 6178, CABA, CP 1322, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios) (importe: 1350000.00) (subtotal: 1350000) (monto_preferido: 1350000) }</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1350000</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>283500</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>94500000000000</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>07/08/2025</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>marinaro.leonelatgmail.com</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1000125892</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0766-23869703</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>30526124916</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>IVA Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Carlos Maria Della Paolera 261 - 4º piso C1001ADA - C.A.B.A. - Argentina</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>30-11048657-6</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>IVA Responsable</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Av. Corrientes 2540
+CABA</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios) (importe: 40004000) (monto_preferido: 40004000) }</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>marinaro.leonelatgmail.com</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1000125890</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NOTA DE DÉBITO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>3217-45753354</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>07/04/2025</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>30708035633</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Rula 7 km 1048, San Luis Capital</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>30-20659736-5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Gral. Hornos 690
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>{ (detalle: None) (importe: 74200.00) (subtotal: 74200.00) (monto_preferido: 74200.00) } { (detalle: Servicios) }</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>38115400000000</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>14/07/2025</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>marinaro.leonelatgmail.com</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1000125891</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>3183-90428147</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>23/04/2025</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>33715065539</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Av. San Juan 2893, 1322, CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Responsable inscripto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>{ (detalle: SERVICIOS) (importe: 879137.73) (subtotal: 879137.73) (monto_preferido: 879137.73) }</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>879.137,73</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>184618,92</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>60697900000000</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>05/03/2025</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>marinaro.leonelatgmail.com</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1000125893</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>7027-83357158</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>28/06/2025</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>33690789499</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Av. Caseros 6178, CABA, CP 1322, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios) (importe: 1734000.00) (subtotal: 1734000) (monto_preferido: 1734000) }</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1734000</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>364140</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>20300000000000</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>07/08/2025</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>aylencopiacopiaseguridadatgmail.com</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1000253279</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>3015-02099443</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>30715636545</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Av. Corrientes 2540 (C1016ACA) Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>I.V.A. Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>{ (detalle: Monthly services) (importe: 750) (subtotal: 750.00) (monto_preferido: 750.00) }</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>750,00</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>157,50</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>93248070166701</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>15/05/2023</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>aylencopiacopiaseguridadatgmail.com</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1000253276</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0009-56411027</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>28/05/2025</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>30741612341</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Av. Santa Fe 110, CABA</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>30526124916</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Carlos Maria Della Paolera 261 - 4º piso C1001ADA - C.A.B.A. - Argentina</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>15.937,06</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>3.346,78</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>478,11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>aylencopiacopiaseguridadatgmail.com</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1000253277</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>aylencopiacopiaseguridadatgmail.com</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1000253280</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0982-28783157
+30-65676017-2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>06/07/2025</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>30656760172901</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Servicios asesoramiento</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Carlos M.
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>{ (detalle: None) (importe: 500000) (monto_preferido: 500000) }</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>608.750,00</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>65.134.312.075.541,</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>17/06/2025</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>aylencopiacopiaseguridadatgmail.com</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1000253278</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>3015-02099443</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>I.V.A Responsable lescript</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Av Corrientes 2540 (C1015ACA) Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>30-71563654-5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>261 17º Piso
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>{ (detalle: None) (importe: 750) (monto_preferido: 750) }</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>750,00</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>93248070166701</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>15/05/2023</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>aylencopiacopiaseguridadatgmail.com</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1000253274</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>aylencopiacopiaseguridadatgmail.com</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1000253275</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0009-56411027</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>28/05/2025</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>30741612341</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Av. Santa Fe 410, CABA</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>30526124916</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Carlos Maria Della Paolera 261 - 4º piso C1001ADA - C.A.B.A. - Argentina</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>{ (detalle: None) (importe: 20) (subtotal: 2300.70) (monto_preferido: 2300.70) } { (detalle: None) (subtotal: 13636.36) (monto_preferido: 13636.36) } { (detalle: None) (importe: 272) (subtotal: 15937.06) (monto_preferido: 15937.06) }</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>3.346,78</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>478,11</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>19.761,95</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>aylencopiacopiaseguridadatgmail.com</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1000253272</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>301502099443</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Av. Corrientes 2540 (C1016ACA)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>I.V.A. Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>750,00</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>157,50</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>93248070166701</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>15/05/2023</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>aylencopiacopiaseguridadatgmail.com</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1000253273</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>758 75855</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>joehenrriatgmail.com</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1000300926</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0766-85345472</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>25/03/2025</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>30526124916</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>IVA Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Carlos Maria Della Paolera 261 - 4º piso C1001ADA - C.A.B.A. - Argentina</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>30-11048657-6</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>IVA Responsable</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Av. Corrientes 2540
+CABA</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios) (importe: 4500) (monto_preferido: 4500) }</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>joehenrriatgmail.com</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1000300927</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1260-10693761</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>30/06/2025</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>27422260930</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Responsable Monotributo</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Erezcano 1029 - Adrogue, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>30-27114647-0</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Responsabe Inscripto</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Av Rivadavia 12980
+Ciudadela, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios de diseño grafico y manejo de redes) (importe: 850000.00) (subtotal: 850000.00) (monto_preferido: 850000.00) }</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>850000</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>178500</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>62200000000000</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>martobargatgmail.com</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>joehenrriatgmail.com</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1000300924</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0007-62112773</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>22/05/2025</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>30741612341</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Av. Santa Fe 410, CABA</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>30526124916</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Carlos Maria Della Paolera 261 - 4º piso C1001ADA - C.A.B.A. - Argentina</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>{ (detalle: 1×2.395,87 / 20) (subtotal: 2300.70) (alicuota_iva: 20) (alicuota_iva_fuente: detalle) (importe_iva_calc: 460.14) (monto_preferido: 2300.70) } { (detalle: None) (importe: 272) (subtotal: 13636.36) (monto_preferido: 13636.36) }</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>15.937,06</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>3.346,78</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>478,11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>joehenrriatgmail.com</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1000300927</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1260-10693761</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>30/06/2025</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>27422260930</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Responsable Monotributo</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Erezcano 1029 - Adrogue, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>30-27114647-0</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Responsabe Inscripto</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Av Rivadavia 12980
+Ciudadela, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios de diseño grafico y manejo de redes) (importe: 850000.00) (subtotal: 850000.00) (monto_preferido: 850000.00) }</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>850000</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>178500</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>62200000000000</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>joehenrriatgmail.com</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1000300925</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3183-69159239</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>14/02/2023</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>33715065539</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Av. San Juan 2893, 1322, CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Responsable inscripto</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>{ (detalle: SERVICIOS) (importe: 69300) (subtotal: 69300.00) (monto_preferido: 69300.00) }</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>69.300,00</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>14553,00</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>92251700000000</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>24/02/2023</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>joehenrriatgmail.com</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1000300926</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0766-85345472</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>25/03/2025</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>30526124916</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>IVA Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Carlos Maria Della Paolera 261 - 4º piso C1001ADA - C.A.B.A. - Argentina</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>30-11048657-6</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>IVA Responsable</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Av. Corrientes 2540
+CABA</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios) (importe: 4500) (monto_preferido: 4500) }</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>martobargatgmail.com</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Consultora Integral S.A.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>leonardo.a.caraccioloatgmail.com</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HIPOLITO YRIGOYEN 372</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>amiriarteatdeloitte.com</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1000118977</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8658-39983744</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>30715691987</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>No responsable</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Av. Las Heras 150, CADA, CP 1228, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>10-67612401-0</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Iva Responsable Inscrição</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Carlos M Della Pastora 261 17' Piso
+CADA, Quenos Aires</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>184618,9233</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>6593,532975</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>48563700000000</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>amiriarteatdeloitte.com</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1000118982</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1054-80474690</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>29/06/2025</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>30546741253</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>IVA Responsable inscripto</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>HIPOLITO YRIGOYEN 371
+1814- Cañuelas- Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Responsable Incripto</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Carlos M. Dolla Paolera 261 17º Piso
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>{ (detalle: Total Valor Plan De) (importe: 1149481) (subtotal: 1149481) (monto_preferido: 1149481) }</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1.149.481,00</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>120.695,51</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>17609675053080</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>09/07/2025</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>amiriarteatdeloitte.com</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1000118978</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0766-73447852</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>02/06/2025</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>30526124916</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>IVA Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Carlos Maria Della Paolera 261 - 4º piso C1001ADA - C.A.B.A. - Argentina</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>30-11048657-6</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>IVA Responsable</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Av. Corrientes 2540
+CABA</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>{ (detalle: None) (importe: 3500) (monto_preferido: 3500) } { (detalle: None) (importe: 3500) (monto_preferido: 3500) }</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>amiriarteatdeloitte.com</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1000118980</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1260-10563337</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>10/05/2025</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>27427250930</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Comune 10F1 - Adragus, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>36-779566674</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Av Rivadavia 12580 Ciudadela, Buenos Aires
+endedes Faro 8 5
+Responesbe Inparis</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios de diseño grafico y manejo de redes) (importe: 950000.00) (subtotal: 950000.00) (monto_preferido: 950000.00) }</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>950000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>199500</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>47900000000000</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>amiriarteatdeloitte.com</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1000118979</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3183-37310108</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>14/04/2025</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>33715065639</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Av. San Juan 2893, 1322, CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>{ (detalle: Codigo Servicio\nSERVICIOS) (importe: 326592.56) (subtotal: 326592.56) (monto_preferido: 326592.56) }</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>68584,44</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2.449,44</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>87676000000000</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>24/04/2025</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/storage/workspaces/facturas/documents/Facturas_totales.xlsx
+++ b/storage/workspaces/facturas/documents/Facturas_totales.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU3"/>
+  <dimension ref="A1:AU16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,6 +1007,2153 @@
         <v>1</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\tolabaseba17\169_5100052264.pdf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tolabaseba17@gmail.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\tolabaseba17\169_5100052264.pdf</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FACTURA
+FACTURA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5703-00127804</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>24/04/2023</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3371751305933717513059</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO
+I.V.A.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SENADOR FERRO 1775 SANTOS LUGARES 1676 Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>30-71239962-3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ING BUTTY 240 PISO 13 240 13</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>LOGISTICA Y DISTRIBUCION VANGES S.R</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>{ (detalle: VILLA DEL SUR BOTELLON 20LTS PALLET\n125861\n8 PACK) (importe: 1170.660) (monto_preferido: 1170.660) } { (detalle: VILLA DEL SUR BOTELLON 20LTS PALLET\n125861\n******** 8 PACK) (importe: 1170.660) (subtotal: 9365.28) (alicuota_iva: 8) (alicuota_iva_fuente: detalle) (importe_iva_calc: 749.22) (monto_preferido: 9365.28) } { (detalle: VILLA DEL SUR BOTELLON 20LTS PALLET\n125861) (cantidad: 8) (importe: 1170.660) (monto_preferido: 1170.660) } { (detalle: VILLA DEL SUR BOTELLON 20LTS PALLET\n125861) (importe: 1170.660) (monto_preferido: 1170.660) }</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>$9.365,28</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>33159100800374
+33159100800374</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>30/04/2023</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>$11.487,22</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>$9.365,28
+$70,24</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>CODIGO Nº 001</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>A
+A</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Aguas de Origen S.A.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\tolabaseba17\170_5100053369.pdf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tolabaseba17@gmail.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\tolabaseba17\170_5100053369.pdf</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>00005 - 00005158</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>06/06/2023</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>30705534752</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>IVA: Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Av Del libertador 7395 Capital Federal</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>30-71239962-3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>BUTTY ENRIQUE ING. 240 Piso: 13 Capital Federal</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ABBVIE S.A.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>{ (detalle: TIT\nTitulares) (cantidad: 49) (importe: 9917.36) (subtotal: 485950.64) (monto_preferido: 485950.64) }</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>485.950,64
+485.950,64</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>102.049,63</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>102.049,63</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Nº73232660346131</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>16/06/2023</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>591.644,90</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Código Nro 001</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Corporate Fitness S.A.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\tolabaseba17\171_5100052264.pdf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>tolabaseba17@gmail.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\tolabaseba17\171_5100052264.pdf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FACTURA
+FACTURA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5703-00127804</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>24/04/2023</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3371751305933717513059</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO
+I.V.A.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SENADOR FERRO 1775 SANTOS LUGARES 1676 Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>30-71239962-3</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ING BUTTY 240 PISO 13 240 13</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>LOGISTICA Y DISTRIBUCION VANGES S.R</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>{ (detalle: VILLA DEL SUR BOTELLON 20LTS PALLET\n125861\n8 PACK) (importe: 1170.660) (monto_preferido: 1170.660) } { (detalle: VILLA DEL SUR BOTELLON 20LTS PALLET\n125861\n******** 8 PACK) (importe: 1170.660) (subtotal: 9365.28) (alicuota_iva: 8) (alicuota_iva_fuente: detalle) (importe_iva_calc: 749.22) (monto_preferido: 9365.28) } { (detalle: VILLA DEL SUR BOTELLON 20LTS PALLET\n125861) (cantidad: 8) (importe: 1170.660) (monto_preferido: 1170.660) } { (detalle: VILLA DEL SUR BOTELLON 20LTS PALLET\n125861) (importe: 1170.660) (monto_preferido: 1170.660) }</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>$9.365,28</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>33159100800374
+33159100800374</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>30/04/2023</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>$11.487,22</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>$9.365,28
+$70,24</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>CODIGO Nº 001</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>A
+A</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Aguas de Origen S.A.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\jmarzol\172_1000096510.jpg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>jmarzol@bago.com.ar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\jmarzol\172_1000096510.jpg</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NOTA DE DÉBITO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3217-72281188</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>07/04/2025</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>30708035633</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Rula 7 km 1048, San Luis Capital</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>30-20859738-8</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>IVA RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Gral. Hornos 690
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Forestal Federal S.A.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios) (importe: 590220.00) (subtotal: 590220.00) (monto_preferido: 590220.00) }</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>590220</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>123946,2</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>94172900000000</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>14/07/2025</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>718592,85</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>4426,65</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>COD. 02</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>TETA TURISMO</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\abg.vmartinez\173_IMG-20250821-WA0004.jpg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>abg.vmartinez@gmail.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\abg.vmartinez\173_IMG-20250821-WA0004.jpg</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\abg.vmartinez\173_IMG-20250821-WA0005.jpg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>abg.vmartinez@gmail.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\abg.vmartinez\173_IMG-20250821-WA0005.jpg</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>IDea&lt;
+&gt; Impu</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\aiannitto\174_20250821_115337.jpg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>aiannitto@msuenergy.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\aiannitto\174_20250821_115337.jpg</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7027-34070766</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>30 48110/43-4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Lnonline
+Av Libertador 372 Lomas de Zamora, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Ano Financier S.A</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>{ (detalle: Servicios) (importe: 1400000.00) (subtotal: 1400000) (monto_preferido: 1400000) }</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1400000</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>294000</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>20700000000000</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>07/08/2025</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>1704500</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>10500</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Cana M° .</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\mfernandab26\175_20250821_115842.jpg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mfernandab26@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\mfernandab26\175_20250821_115842.jpg</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5779-09592800</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>25/04/2025</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>30626675626</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Av. Libertador 6434, CABA, CP 1520, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Incripto</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>DELOITTE &amp; Co. S.A</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>{ (detalle: ASESORAMIENTO CONTABLE) (importe: 331762.00) (subtotal: 331762.00) (monto_preferido: 331762.00) }</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>331762</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>54474500000000</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2488,215</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>69670,02</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Codigo 001</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>Milenium Soft S.A</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\fgborri\176_image0.jpeg</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fgborri@gmail.com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\fgborri\176_image0.jpeg</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>REMITO-FACTURA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8480-19723924</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SC717616525</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>30-52632495-6</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Cantos M. Dela Paolera 26: 17" Pao
+CARA, Argentina</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>DELCHTTE &amp; Co. S.A</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>{ (detalle: ALMENDRA PEL X 19 KG. VAREDADES) (cantidad: 15) (importe: 88000.00) (alicuota_iva: 19) (alicuota_iva_fuente: detalle) (importe_iva_calc: 16720.00) (monto_preferido: 88000.00) }</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>35948339997048</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>1BOT180</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Cod 1</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\mpaulamoreira\177_image0.jpeg</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>mpaulamoreira@yahoo.com.ar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\mpaulamoreira\177_image0.jpeg</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>REMITO-FACTURA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8650-19723924</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>30717616525</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>L.V.A. Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Av. Santa Fe 3400, CABA</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>DELOITTE &amp; Co. S.A</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>{ (detalle: ALMENDRA PEL. X 10 KG. VARIEDADES) (cantidad: 15) (importe: 88000.00) (subtotal: 1320000.00) (alicuota_iva: 10) (alicuota_iva_fuente: detalle) (importe_iva_calc: 132000.00) (monto_preferido: 1320000.00) }</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1320000</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>277200</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>35948333997048</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>21/06/2025</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>1607100</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>9900</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Cod.1</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Cerealera Parandi S.A.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\vgperalta2\178_archivo adjunto 1.pdf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>vgperalta2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\vgperalta2\178_archivo adjunto 1.pdf</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0300-25808736</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>05/12/2023</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>30703948983</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Av. Belgrano 9018, CABA, CP 1511, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>DELOITTE &amp; Co. S.A</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>67799900000000</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>67799900000000</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>22/05/2023</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Codigo</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>Soluciones Integrales S.A.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\Graciela.Torrez\179_1000129358.jpg</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Graciela.Torrez@seaboard.com.ar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\Graciela.Torrez\179_1000129358.jpg</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5779-09592800</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>25/04/2025</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>30626675626</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Av. Libertador 6434, CABA, CP 1520, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Incripto</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>DELOITTE &amp; Co. S.A</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>{ (detalle: ASESORAMIENTO CONTABLE) (importe: 331762.00) (subtotal: 331762.00) (monto_preferido: 331762.00) }</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>331762</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>69670,02</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>54474500000000</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>403920,235</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2488,215</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Codigo 001</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Milenium Soft S.A</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+      <c r="AU15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\silvina.sanguine\180_PHOTO-2025-08-21-12-00-02.jpg</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>silvina.sanguine@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>adjuntos_gmail\descargas\silvina.sanguine\180_PHOTO-2025-08-21-12-00-02.jpg</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5779-09592800</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>25/04/2025</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>30626675626</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Av. Libertador 6434, CABA, CP 1520, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>30-52612491-6</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Incripto</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Carlos M. Della Paolera 261 17º Piso
+CABA, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>DELOITTE &amp; Co. S.A</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>{ (detalle: ASESORAMIENTO CONTABLE) (importe: 331762.00) (subtotal: 331762.00) (monto_preferido: 331762.00) }</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>331762</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>54474500000000</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>2488,215</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>69670,02</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Codigo 001</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Milenium Soft S.A</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>arg_invoice_5</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
